--- a/inputs/portfolio_input_blank.xlsx
+++ b/inputs/portfolio_input_blank.xlsx
@@ -535,7 +535,7 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>In de outputbestanden staat een extra tabblad "output". Daarin staan de doorgerekende portefeuillegewichten met direct daaronder de statistieken. De mean-variance frontier wordt in de notebook geplot en niet als tabel in Excel opgenomen.</t>
+          <t>In de outputbestanden staat een extra tabblad "output". Daarin staan de doorgerekende portefeuillegewichten met direct daaronder de statistieken. De frontier-punten staan in dezelfde tabel achter de portefeuilles. De frontier-plot wordt in de notebook gemaakt.</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -733,7 +733,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Duitse Staatsobligaties</t>
+          <t>Direct Lending Europa</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -743,7 +743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMD HC</t>
+          <t>Duitse Staatsobligaties</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -753,7 +753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMD LC</t>
+          <t>EMD HC</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -763,7 +763,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Euro IG Credits</t>
+          <t>EMD LC</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -773,7 +773,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Euro ILBs</t>
+          <t>Euro IG Credits</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -783,7 +783,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Euro Staatsobligaties</t>
+          <t>Euro ILBs</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -793,7 +793,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global High Yield</t>
+          <t>Euro Staatsobligaties</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -803,7 +803,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global IG Credits</t>
+          <t>Global High Yield</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -813,7 +813,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global ILBs</t>
+          <t>Global IG Credits</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -823,7 +823,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grondstoffen</t>
+          <t>Global ILBs</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -833,7 +833,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
+          <t>Grondstoffen</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -843,7 +843,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Internationaal Privaat Vastgoed</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italisaanse Staatsobligaties</t>
+          <t>Internationaal Privaat Vastgoed</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -863,7 +863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nederlandse Hypotheken</t>
+          <t>Italisaanse Staatsobligaties</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Privaat Infrastructuur</t>
+          <t>Nederlandse Hypotheken</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
@@ -883,7 +883,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Privaat Vastgoed NL</t>
+          <t>Privaat Infrastructuur</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -893,10 +893,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Privaat Vastgoed NL</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B27" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -911,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1081,7 +1091,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Duitse Staatsobligaties</t>
+          <t>Direct Lending Europa</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -1095,7 +1105,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMD HC</t>
+          <t>Duitse Staatsobligaties</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -1109,7 +1119,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMD LC</t>
+          <t>EMD HC</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -1123,7 +1133,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Euro IG Credits</t>
+          <t>EMD LC</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -1137,7 +1147,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Euro ILBs</t>
+          <t>Euro IG Credits</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
@@ -1151,7 +1161,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Euro Staatsobligaties</t>
+          <t>Euro ILBs</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
@@ -1165,7 +1175,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global High Yield</t>
+          <t>Euro Staatsobligaties</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
@@ -1179,7 +1189,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global IG Credits</t>
+          <t>Global High Yield</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1193,7 +1203,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global ILBs</t>
+          <t>Global IG Credits</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
@@ -1207,7 +1217,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grondstoffen</t>
+          <t>Global ILBs</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1221,7 +1231,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
+          <t>Grondstoffen</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -1235,7 +1245,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Internationaal Privaat Vastgoed</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -1249,7 +1259,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italisaanse Staatsobligaties</t>
+          <t>Internationaal Privaat Vastgoed</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
@@ -1263,7 +1273,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nederlandse Hypotheken</t>
+          <t>Italisaanse Staatsobligaties</t>
         </is>
       </c>
       <c r="B23" s="5" t="n"/>
@@ -1277,7 +1287,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Privaat Infrastructuur</t>
+          <t>Nederlandse Hypotheken</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
@@ -1291,7 +1301,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Privaat Vastgoed NL</t>
+          <t>Privaat Infrastructuur</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
@@ -1305,7 +1315,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Private Equity</t>
+          <t>Privaat Vastgoed NL</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
@@ -1316,42 +1326,46 @@
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Group_Key</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Group_Name</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Group_1</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Group_2</t>
+          <t>Group_1</t>
         </is>
       </c>
       <c r="B31" s="5" t="n"/>
@@ -1361,7 +1375,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Group_3</t>
+          <t>Group_2</t>
         </is>
       </c>
       <c r="B32" s="5" t="n"/>
@@ -1371,7 +1385,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Group_4</t>
+          <t>Group_3</t>
         </is>
       </c>
       <c r="B33" s="5" t="n"/>
@@ -1381,12 +1395,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Group_5</t>
+          <t>Group_4</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Group_5</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1399,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1513,7 +1537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Duitse Staatsobligaties</t>
+          <t>Direct Lending Europa</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -1523,7 +1547,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMD HC</t>
+          <t>Duitse Staatsobligaties</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -1533,7 +1557,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMD LC</t>
+          <t>EMD HC</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -1543,7 +1567,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Euro IG Credits</t>
+          <t>EMD LC</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -1553,7 +1577,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Euro ILBs</t>
+          <t>Euro IG Credits</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
@@ -1563,7 +1587,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Euro Staatsobligaties</t>
+          <t>Euro ILBs</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
@@ -1573,7 +1597,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global High Yield</t>
+          <t>Euro Staatsobligaties</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
@@ -1583,7 +1607,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global IG Credits</t>
+          <t>Global High Yield</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1593,7 +1617,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global ILBs</t>
+          <t>Global IG Credits</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
@@ -1603,7 +1627,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grondstoffen</t>
+          <t>Global ILBs</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1613,7 +1637,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
+          <t>Grondstoffen</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -1623,7 +1647,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Internationaal Privaat Vastgoed</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -1633,7 +1657,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italisaanse Staatsobligaties</t>
+          <t>Internationaal Privaat Vastgoed</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
@@ -1643,7 +1667,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nederlandse Hypotheken</t>
+          <t>Italisaanse Staatsobligaties</t>
         </is>
       </c>
       <c r="B23" s="5" t="n"/>
@@ -1653,7 +1677,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Privaat Infrastructuur</t>
+          <t>Nederlandse Hypotheken</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
@@ -1663,7 +1687,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Privaat Vastgoed NL</t>
+          <t>Privaat Infrastructuur</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
@@ -1673,12 +1697,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Private Equity</t>
+          <t>Privaat Vastgoed NL</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
